--- a/deliverables/上海AI博物馆_投资盈利政策落地表.xlsx
+++ b/deliverables/上海AI博物馆_投资盈利政策落地表.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_盈利模式" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_政策扶持" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_场地候选" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_展陈资源" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_内容资源" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_组织分工" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_风险台账" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_资方对接跟踪" sheetId="10" state="visible" r:id="rId10"/>
@@ -583,14 +583,14 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>上海AI博物馆（全产业链常态化展示与孵化平台） · 落地总览</t>
+          <t>上海AI博物馆（产业展示与孵化运营平台） · 落地总览</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>V1.0 | 2026-08-10 | 核心：投资路径 / 盈利模式 / 政策扶持</t>
+          <t>V1.1 | 2026-08-10 | 核心：投资路径 / 盈利模式 / 政策扶持</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>科协牵头、多主体出资建设「AI全产业链博物馆」，项目方轻资产运营：用场地免租+设备配套+赞助捐赠完成建设，用租金/研学/孵化/模板输出/海外内容实现盈利。</t>
+          <t>多方合作建设人工智能产业相关常设展馆与配套服务空间：以租金优惠/装修共担、赞助展位、专项补贴与运营公司启动金完成开办；以空间经营、研学服务、展位赞助实现可持续收入。</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>投资方如何出资／入场（场地免费期、设备装修金、赞助层级、股权孵化）</t>
+          <t>投资方如何出资／入场（租金与装修共担、赞助层级、引导基金与跟投）</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>项目如何持续盈利（租金运营、孵化投资、模板输出、研学、海外内容变现）</t>
+          <t>项目如何持续盈利（空间经营、研学服务、孵化收益、可复制运营输出）</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>政策性支持如何落地（教育部研学强制要求、科协牵头、政府场地与扶持基金）</t>
+          <t>政策性支持如何落地（教育研学、科普专项、科创扶持、闲置物业盘活）</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -744,7 +744,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>0. 材料与共识</t>
+          <t>0. 材料与测算</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>极简BP、投资/盈利/政策一页纸、预算框架</t>
+          <t>极简BP、投资/盈利/政策一页纸、一期预算框架</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>群内定稿可外发</t>
+          <t>可外发且数字自洽</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>两处场地+华润/区政府/科协路演纪要</t>
+          <t>两处场地+潜在赞助/区平台路演纪要</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>至少1个场地框架意向</t>
+          <t>至少1份可谈判租约/合作要点</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2. 签约绑定</t>
+          <t>2. 条款绑定</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>场地免租+出资协议、科协合作文件、主赞助意向</t>
+          <t>租约与装修分摊、主赞助意向、关键专项申报启动</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>建设资金与场地封闭</t>
+          <t>开办资金来源可覆盖预算</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -831,22 +831,22 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>3. 展陈与装修</t>
+          <t>3. 设计与装修</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>3–9月</t>
+          <t>租约后3–9月</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>动线施工图、展品清单签约、开馆内容包</t>
+          <t>施工图、展位清单签约、开业内容包</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>试运行接待</t>
+          <t>通过试运行接待</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -860,22 +860,22 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>4. 开馆运营</t>
+          <t>4. 开业运营</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>开馆后0–12月</t>
+          <t>开业后0–12月</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>研学排期、招商出租率、内容周更</t>
+          <t>研学排期、可租面积去化、赞助履约</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>达对标接待与出租率</t>
+          <t>达到预算约定的经营指标</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -889,22 +889,22 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>5. 复制准备</t>
+          <t>5. 优化扩展</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>开馆后12月+</t>
+          <t>开业后12月+</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>SOP与模板包、外埠意向</t>
+          <t>SOP沉淀；评估是否外拓咨询</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>首个输出合同</t>
+          <t>数据驱动决策</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>主赞助/场地</t>
+          <t>主赞助/战略</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>B / A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       <c r="F5" s="7" t="inlineStr"/>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>同学通道材料</t>
+          <t>立项对齐</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -1132,7 +1132,7 @@
       <c r="F6" s="8" t="inlineStr"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>免租+5000万</t>
+          <t>租金与装修分摊</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -1172,7 +1172,7 @@
       <c r="F7" s="7" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>产权与改造</t>
+          <t>产权与改造估算</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1190,12 +1190,12 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>中国科协</t>
+          <t>中国科协/地方科协</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>主管/专项</t>
+          <t>社团合作</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>汇报材料</t>
+          <t>备忘录材料</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>已初步沟通</t>
+          <t>已有初步沟通</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>重点项目申报</t>
+          <t>专项申报</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -1266,12 +1266,12 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>头部大模型企业（沪）</t>
+          <t>在沪科技企业</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>金牌赞助</t>
+          <t>展位合作</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -1284,7 +1284,7 @@
       <c r="F10" s="8" t="inlineStr"/>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>展席权益</t>
+          <t>展位权益</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -1302,30 +1302,34 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>曾达</t>
+          <t>海外授权线索</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>生态合作</t>
+          <t>内容授权</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>C/G</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>陈胜</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>角色定义</t>
+          <t>授权可行性</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>邀约</t>
+          <t>线索清单</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -1338,30 +1342,34 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>海外科技企业</t>
+          <t>教育/研学渠道</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>内容授权</t>
+          <t>B端客群</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>陈红苗</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="inlineStr"/>
       <c r="F12" s="8" t="inlineStr"/>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>接受度/合规</t>
+          <t>基地目录</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>陈院长清单</t>
+          <t>课程备案</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
@@ -1529,7 +1537,7 @@
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>两场沟通围绕「在上海筹建AI博物馆」展开：场次一明确全产业链展陈、教育部认证与研学切入、华润等赞助商与海外变现思路；场次二由陈院长提出完整方案，就项目定位、场地、资金、盈利、科协牵头与分工达成共识，约定会后整理可展示方案并分别对接场地与资方。</t>
+          <t>两场沟通围绕「在上海筹建AI相关产业展馆」展开：场次一讨论教育研学切入、赞助合作与内容运营方向；场次二由陈胜提出整体框架，与胡继刚、陈红苗就项目定位、场地、资金、盈利与分工交换意见，约定会后整理可对外材料，并分头对接场地与资方。</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1568,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>对标美国计算机历史博物馆；打造世界人工智能大会闭幕后的365天常态化AI展示平台；抢占「AI博物馆」名称IP；覆盖芯片算力—技术应用—具身/移动AI全产业链。</t>
+          <t>参考成熟科技类博物馆的常设展运营方式，定位为人工智能产业相关的常设展示与配套服务空间；内容覆盖算力基础设施、模型与行业应用等可核验的产业环节，并与城市重大展会形成会后延伸，而非一过性临展。</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1580,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>教育部要求中学阶段开展AI培训与研学（约需培训1万名AI老师），研学带有强制性；AI教育产品需强制认证，可先在上海完成国产AI统一认证；切入时机为AI应用元年。</t>
+          <t>中小学人工智能相关教育、教师研修与研学活动存在明确需求，可争取纳入区级研学/科普基地目录；教育类产品与场地服务需符合主管部门规范。市场机会存在，但「强制刚需」不宜作为商务承诺写入对外材料，应以备案与采购合同落地为准。</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1592,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>总面积约6000–10000㎡（亦提及5000–10000㎡）；1–2层约2000㎡作展馆，其余作孵化办公与研学；要求场地方提供10–20年免费用地，并配套约5000万装修与设备资金。</t>
+          <t>一期建议控制在可运营规模：展示区约1500–3000㎡，或先落创智汇约3300㎡顶楼作试点；若后续扩展至更大体量，需单独做投资测算。租金、装修与设备以「共担+分期」谈判，不把长期免租或场地方大额无偿出资作为前提。</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1604,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>①五角场创智汇2号楼顶楼约3300㎡（杨浦科创集团产权、中建四局二房东）；②复兴岛（中环边，距陆家嘴约25分钟车程）。上海闲置场地较多，获取难度相对可控。</t>
+          <t>①五角场创智汇2号楼顶楼约3300㎡（杨浦科创集团产权、中建四局二房东），地段利于研学；②复兴岛相关物业（中环边），改造可塑性强，需先踏勘与改造估算。两处并行比选。</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1616,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>多主体分担、项目方原则上不自掏建设资金；政府补贴、头部AI企业捐赠、产业集团兜底、科协专项；潜在主体含华润（发起人同学资源）、科协牵头、曾达等AI布局方。</t>
+          <t>资金宜多主体组合：场地方/业主租金优惠或装修补贴、主赞助与企业展位合作、政府科创/科普/文旅专项、产业引导基金及运营方自有启动资金。潜在沟通对象含华润等有科创合作意愿的央国企、区属平台与头部科技企业；具体以对方立项流程为准。</t>
         </is>
       </c>
     </row>
@@ -1620,19 +1628,19 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>展馆本身偏捐赠/补贴；收益来自剩余楼层租金与运营服务、入驻项目孵化持股、样板向地方政府模板输出、研学接待、国内应用内容海外账号变现与跨境直播。</t>
+          <t>展陈本身难靠门票覆盖成本；可持续收入优先来自：配套空间租金与活动运营、研学/培训服务、企业展位与赞助、入驻项目服务费及有限跟投、对外运营咨询。跨境外内容变现仅作远期选项，不计入一期必达收入。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>展陈与资源</t>
+          <t>内容与资源</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>美方侧重基础理论（已筛前20项核心展品），中方侧重产业应用；可对接谷歌/微软/Meta等，并联动李飞飞等海外人物直播；国内头部大模型企业多数在沪，对接便利。</t>
+          <t>展陈以可签约的企业展品、可说明的技术演进与行业应用案例为主；海外机构与企业合作按授权与合规推进，不预设「实时连线/名人直播」类不可控事项。国内头部科技与模型相关企业多数在沪，便于集中拜访谈展位合作。</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1652,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>陈院长返美整合硅谷资源并补充材料；胡老师整理可展示文字版；国内团队对接政府/央国企场地资金；邀请曾达；先定大框架与预算，再做动线施工图。</t>
+          <t>陈胜负责海外侧资源线索与方案补充；胡继刚统筹国内文字方案与路演材料；陈红苗配合梳理并分头对接场地与资方；先完成预算框架与合作条款清单，再进入设计深化。</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1693,12 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>陈院长</t>
+          <t>陈胜</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>向项目群发送AI博物馆极简文字材料</t>
+          <t>向项目群发送项目极简文字材料</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1700,7 +1708,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>返美前</t>
+          <t>近期</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1712,12 +1720,12 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>陈院长</t>
+          <t>陈胜</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>返美后整合硅谷资源，对接海外展陈与内容</t>
+          <t>补充海外侧可对接资源清单（授权可行性优先）</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -1739,12 +1747,12 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>陈院长</t>
+          <t>陈胜</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>会见航海博物馆馆长，咨询建馆运营经验</t>
+          <t>会见航海博物馆相关负责人，咨询建馆运营经验</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1766,12 +1774,12 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>胡老师</t>
+          <t>胡继刚</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>整理双场讨论，形成可展示项目版本</t>
+          <t>整理双场讨论，形成可对外项目版本（本套材料）</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -1793,7 +1801,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>说话人1/配合方</t>
+          <t>陈红苗</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -1820,22 +1828,22 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>参会团队</t>
+          <t>胡继刚/陈红苗</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>邀请曾达共同推进</t>
+          <t>与区平台、科协等沟通合作路径与申报窗口</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>近期</t>
+          <t>两周内</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -1847,22 +1855,22 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>国内团队</t>
+          <t>参会团队</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>与科协/地方政府确认牵头与名称IP路径</t>
+          <t>视进展邀请产业侧合作方共同推进</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>两周内</t>
+          <t>按需</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -1919,7 +1927,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>核心策略：「不自有资金站上制高点」——建设与装修改造由合作方承担，项目方以IP运营、资源整合与孵化投资能力换取长期权益；投资结构分层、可组合，避免单一资方绑架。</t>
+          <t>核心策略：建设与运营资金「可组合、可核算、可退出」——以租金优惠/装修共担、赞助与展位、专项补贴和自有启动金构成一期资金盘，避免把超长期零租金或场地方大额无偿出资写成既定条件；项目公司保留运营与品牌权益，投资结构分层，防止单一资方绑架。</t>
         </is>
       </c>
     </row>
@@ -1975,27 +1983,27 @@
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>A. 场地方「地+钱」合作</t>
+          <t>A. 场地方租金与装修共担</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>10–20年免费场地使用权 + 约5000万装修/设备采购资金</t>
+          <t>市场化租金为基础；争取装修期减免或开业后1–3年租金阶梯优惠；装修/基础机电可由业主部分投入，运营方或赞助方补齐，按合同回收或分成</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>拥有闲置物业的央国企/区属平台（如科创集团、华润系物业）</t>
+          <t>拥有可改造物业的区属平台、央国企物业（如科创集团、华润系物业等）</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>政绩亮点（高层考察）、物业盘活、剩余楼层租金分成或优先招商权、品牌冠名可选</t>
+          <t>稳定租金与物业增值、剩余可租面积招商分成、品牌联合与政务参观场景</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>出具需求书→双候选场地路演→签约框架（免租期+出资额+分成公式）</t>
+          <t>需求书+投资测算→双场地比选路演→框架协议（租期、优惠条件、装修分摊、退出）</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -2013,27 +2021,27 @@
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>B. 主赞助商（场地或核心费用）</t>
+          <t>B. 主赞助 / 战略合作出资</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>承担场地租金折算、展陈主投或运营启动金；可现金+实物（展品/算力）</t>
+          <t>现金赞助、展陈主投或运营启动金；可搭配实物（展品、设备）按评估入账</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>华润等有科创投入考核的央国企；有向上汇报「AI故事」需求的产业集团</t>
+          <t>有科创合作与品牌曝光需求的央国企、产业集团</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>主赞助商权益、AI行业历史展席位、联合发布与WAIC联动曝光</t>
+          <t>主赞助权益、联合活动、指定展区露出、年度报告与参访安排</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>一页纸权益包→同学/董事会通道引荐→立项材料对齐其科创KPI</t>
+          <t>一页纸权益包→对接人对齐对方立项KPI→赞助/合作协议</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -2051,27 +2059,27 @@
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>C. 金牌/展席赞助（头部AI企业捐赠）</t>
+          <t>C. 企业展位与内容合作</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>展品捐赠+展位建设费+年度内容更新费；可选现金捐赠换历史席位</t>
+          <t>展位建设费+年度内容更新费；或展品借用/捐赠+基础布展成本分摊</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>国内头部大模型与科技企业（千问/豆包/Kimi/智谱/DeepSeek/MiniMax等，多数在沪）</t>
+          <t>在沪科技与产业应用相关企业（模型、云、硬件、行业方案等）</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>「AI行业历史」永久/长期展示席位、研学流量、政企参观背书</t>
+          <t>展区品牌露出、研学线路露出、政企参访触达</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>编制展席权益清单→上海头部企业集中拜访→捐赠协议+内容更新SLA</t>
+          <t>展位权益清单→集中拜访→展位/内容合作协议（含更新与撤展条款）</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -2094,22 +2102,22 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>场地租金补贴、文旅/科普/科创专项、产业引导基金配套、装修补助</t>
+          <t>租金/装修补助、科普与科创专项、文旅融合项目资助、引导基金配套（若符合）</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>区政府、科创委、文旅局、教育局（研学）、科协系统专项</t>
+          <t>区政府相关部门、科创/经信、文旅、教育、科协系统</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>公共服务供给、研学指标完成、科创政绩与WAIC延伸场景</t>
+          <t>公共服务与科普供给、研学与科创场景、重点项目库政绩</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>政策清单匹配→申报材料包→纳入区重点项目库</t>
+          <t>政策匹配表→材料包→申报与验收台账</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -2127,32 +2135,32 @@
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>E. 科协牵头专项</t>
+          <t>E. 科协等社团合作</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>名义主管+专项经费/科普经费；协助抢占「AI博物馆」名称与资质</t>
+          <t>合作挂牌、科普活动联合、可申报的科普/学术活动经费（以实际批复为准）</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>中国科协及地方科协（发起人已与科协主席初步沟通）</t>
+          <t>中国科协及地方科协（已有初步沟通基础，需走正式文件）</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>行业制高点、科普职能落地、全国复制时的系统内通道</t>
+          <t>专业背书、科普职能落地、活动与传播资源</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>正式汇报材料→名称与主管单位确认→专项申报</t>
+          <t>合作备忘录/请示材料→名称与合作方式确认→按年度申报</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -2165,32 +2173,32 @@
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>F. 孵化跟投（轻资本）</t>
+          <t>F. 运营方启动资金与跟投</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>对入驻优质AI项目小额股权跟投/收益权；可用运营方管理公司主体承接</t>
+          <t>运营公司自有/股东启动金覆盖设计、团队与开业前费用；对入驻优质项目小额跟投另设池</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>项目运营方联合产业资本；亦可引入区引导基金子基金</t>
+          <t>项目运营主体股东；可联合区引导基金子基金</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>长期资本增值；与展馆流量、场景验证形成闭环</t>
+          <t>运营利润分配；跟投项目长期资本回报（不计入开业必达）</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>设立孵化投资SOP→入驻协议含优先投资权→联合区基金</t>
+          <t>明确一期启动金预算→公司主体与治理→跟投SOP（后期）</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -2203,32 +2211,32 @@
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>G. 海外内容与品牌合作</t>
+          <t>G. 授权类内容合作</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>展品授权/内容共建（非现金为主）；联合直播与活动赞助</t>
+          <t>展品/影像授权费或互换资源；活动联合赞助（一事一议）</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>谷歌、微软、Meta、苹果及硅谷高校实验室；海外KOL</t>
+          <t>国内外科技企业、高校实验室、行业机构</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>中国市场曝光、中美双向展示叙事</t>
+          <t>市场曝光与合作叙事（以合同约定为准）</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>陈院长硅谷对接清单→授权模板（中英）→内容剪辑翻译流水线</t>
+          <t>陈胜侧线索清单→授权模板→法务合规审查后落地</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -2253,7 +2261,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>出资门槛（建议）</t>
+          <t>出资门槛（建议，可议）</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -2290,12 +2298,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>场地或≥3000万级核心费用/等值</t>
+          <t>按一期预算单列，建议不低于核心开办费用的显著比例</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>冠名协商权、主视觉露出、开幕式主位、年度联名活动</t>
+          <t>冠名协商、主视觉、开幕主位、年度联名活动</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -2319,17 +2327,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>500–1500万现金/展陈建设+年度更新</t>
+          <t>展区建设+年度更新，或等额现金赞助</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>AI历史展席位、研学指定线路露出、高层参观接待位</t>
+          <t>主要展区露出、研学线路露出、参访接待位</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>6–10</t>
+          <t>若干</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -2343,12 +2351,12 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>展品合作伙伴</t>
+          <t>展位合作伙伴</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>展品捐赠+展位装修</t>
+          <t>展位装修+内容维护</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -2372,17 +2380,17 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>战略渠道伙伴</t>
+          <t>渠道合作伙伴</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>流量/研学渠道/媒体</t>
+          <t>研学/媒体/流量资源</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>渠道分成、联名研学产品</t>
+          <t>渠道分成、联名产品</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -2423,7 +2431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2445,7 +2453,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>展馆本体以「捐赠+补贴+赞助」覆盖建设与基础运营；可核算利润主要来自空间经营、研学与认证相关服务、孵化投资、模板输出与海外内容——用IP把流量与信任变现。</t>
+          <t>一期以「空间经营 + 服务收入 + 赞助」覆盖运营；展陈成本靠赞助、专项与开办资金消化。不把门票、境外账号变现、外埠快速复制写成开业必达项；待运营数据稳定后再扩展。</t>
         </is>
       </c>
     </row>
@@ -2496,17 +2504,17 @@
     <row r="6" ht="50" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>1. 剩余楼层租金与运营服务</t>
+          <t>1. 配套空间租金与运营服务</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>非展陈楼层出租给AI企业办公/展示/路演；收租金+物业/活动运营费，反哺展馆运营。</t>
+          <t>非核心展区或同物业可租面积，用于企业办公、路演、临时展示；收租金与活动运营费。</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>场地签约、完成基础装修与招商手册</t>
+          <t>租约落地、基础装修完成、招商手册发布</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -2516,7 +2524,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>开馆12个月内出租率≥70%</t>
+          <t>开业12个月内可租面积去化达标（指标在预算中单列）</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -2529,17 +2537,17 @@
     <row r="7" ht="50" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2. 研学与培训接待</t>
+          <t>2. 研学与培训服务</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>对接教育部研学强制要求与AI教师培训；分班接待学生/家长（可设6班制），B端学校与机构采购。</t>
+          <t>面向学校与机构的研学接待、教师研修配套服务；按场次/人次/包场报价。</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>展陈开放+课程包+安全预案；争取纳入区研学目录</t>
+          <t>展陈开放、课程与安全预案、争取进入区研学/科普目录</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2549,7 +2557,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>对标现有机器人展厅「上午三场下午三场」接待强度</t>
+          <t>完成首个完整学期的排期与回款</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -2562,27 +2570,27 @@
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>3. 认证与教育产品服务</t>
+          <t>3. 企业展位与活动赞助</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>借力AI教育产品强制认证，提供展示验证、场景测评、认证辅导等增值服务。</t>
+          <t>常设展位费、临展与发布活动场地服务、品牌赞助包。</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>上海统一认证路径明确、与教育主管部门沟通</t>
+          <t>权益包与价目表定稿、首批意向客户签约</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>5–10%</t>
+          <t>15–25%</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>首批10个合作单元落地</t>
+          <t>开业时主赞助+不少于约定数量的展位合同</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -2595,27 +2603,27 @@
     <row r="9" ht="50" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>4. 孵化投资收益</t>
+          <t>4. 园区/入驻服务费</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>对入驻优质项目持股或收益权，获取长期资本回报。</t>
+          <t>为入驻团队提供商务、活动、对接等服务，收取服务费；股权跟投另册管理。</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>入驻协议含投资条款；可选设小规模跟投池</t>
+          <t>入驻协议模板、服务清单与定价</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>10–20%（波动大）</t>
+          <t>5–10%</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>每年重点跟投3–5个项目</t>
+          <t>首批入驻签约</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -2628,27 +2636,27 @@
     <row r="10" ht="50" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>5. 样板模板输出</t>
+          <t>5. 运营咨询与模式输出（后期）</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>上海做成标准后，向其他地方政府输出「AI博物馆」建设与运营模板（咨询+品牌授权+落地陪跑）。</t>
+          <t>在上海验证运营后再对外提供筹建咨询与运营陪跑，不作为一期收入承诺。</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>开馆运营满1个完整研学季、沉淀SOP与IP</t>
+          <t>本地运营满至少一个完整财年并沉淀SOP</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>10–15%</t>
+          <t>0–10%（后期）</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>首个外埠复制意向框架协议</t>
+          <t>首单外部咨询合同（可选）</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -2658,87 +2666,77 @@
       </c>
       <c r="G10" s="8" t="inlineStr"/>
     </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>6. 海外内容变现</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>国内应用层成果拍成视频反向输出海外账号；硅谷/斯坦福成果直播；汇率与付费意愿更优。</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>内容团队+海外账号矩阵+授权合规</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>5–10%</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>稳定周更+单场直播商业化</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>空间与经济假设（讨论稿）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>口径说明</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>参考区间（讨论稿）</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>参考区间（讨论稿，待测算锁定）</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>确认状态</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>物业合作</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>租期与租金条件</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>市场租金可谈；争取装修期减免或1–3年阶梯优惠</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>场地方投入</t>
+          <t>装修与设备</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>免租期折算+装修设备</t>
+          <t>开办资本性支出</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>免租10–20年 + 约5000万设备装修</t>
+          <t>按方案级估算后报资方，业主/赞助/自有资金共担</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2751,17 +2749,17 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>展馆面积</t>
+          <t>展示面积（一期）</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>1–2层展示</t>
+          <t>可运营展示区</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>约2000㎡</t>
+          <t>约1500–3300㎡（创智汇顶楼可作一期）</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -2774,17 +2772,17 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>经营面积</t>
+          <t>配套经营面积</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>孵化办公等</t>
+          <t>可租/可活动面积</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>总建约6000–10000㎡中的非展部分</t>
+          <t>视最终选址物业条件确定</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -2797,17 +2795,17 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>对标接待</t>
+          <t>运营周期假设</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>曹河泾/张江机器人展厅</t>
+          <t>商务计划口径</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>日均上午3场+下午3场研学</t>
+          <t>首期租约建议对标5年左右，含中期评估与续约条款</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -2820,17 +2818,17 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>运营周期</t>
+          <t>项目公司资金</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>长期价值</t>
+          <t>开办与运营</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>至少5–10年</t>
+          <t>须单列启动金与12–18个月运营储备，不可假设为零</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -2839,39 +2837,16 @@
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>项目方建设出资</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>原则</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>建设期尽量为0；运营公司轻资产</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F6:F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6:F10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未开始,进行中,已完成,阻塞,取消"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2885,7 +2860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2958,27 +2933,27 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>教育部中学AI培训与研学要求</t>
+          <t>中小学人工智能相关教育与研学</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>中学开展AI培训；约1万名AI教师培训需求；学生研学带强制性</t>
+          <t>地方推进相关教育与研学活动，存在基地与课程合作空间</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>刚性客流与B端采购</t>
+          <t>B端团客与课程服务收入</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>纳入区研学基地目录→课程与师资包备案→学校采购合同</t>
+          <t>申报区研学/科普基地→课程备案→学校/机构采购合同</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>国内运营+教育渠道</t>
+          <t>陈红苗+教育渠道</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -2991,27 +2966,27 @@
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>AI教育产品强制认证</t>
+          <t>教育与科普场馆规范</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>相关产品须认证；可先做上海国产AI统一认证场景</t>
+          <t>场地服务与教育活动需符合主管部门要求</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>展馆成为认证展示与验证场</t>
+          <t>合规展陈与可售服务前提</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>对接认证主体→设立认证展示专区→服务产品报价</t>
+          <t>梳理准入清单→必要时对接认证/备案主体→服务产品合规化</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>产品+政府关系</t>
+          <t>运营+政府关系</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -3024,27 +2999,27 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>中国科协牵头主管</t>
+          <t>科协等社团合作挂牌</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>名正言顺抢占IP；已与科协主席初步沟通</t>
+          <t>已有初步沟通，需正式文件明确合作方式</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>名称、资质、全国复制通道</t>
+          <t>专业背书与科普活动资源</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>正式请示/合作备忘录→名称核准路径→科普专项申报</t>
+          <t>合作备忘录→挂牌与活动计划→按年度申报可获经费</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>发起人+胡老师材料</t>
+          <t>陈胜线索+胡继刚材料</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -3057,22 +3032,22 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>地方政府科创政绩与闲置物业盘活</t>
+          <t>闲置物业盘活与租金支持</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>高层考察、WAIC延伸、闲置楼宇去化</t>
+          <t>区属/国企物业去化，可能有租金优惠或装修支持政策</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>免租场地+装修配套资金谈判筹码</t>
+          <t>降低开办期租金与改造压力（以批复为准）</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>区领导汇报→重点项目入库→土地/物业会议纪要</t>
+          <t>区领导/平台汇报→政策适用性确认→写入租约附件</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3090,22 +3065,22 @@
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>区级/市级科创与文旅扶持资金</t>
+          <t>区级/市级科创与文旅专项</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>产业扶持、科普场馆、文旅融合、中小企业创新等可组合申报</t>
+          <t>产业扶持、科普场馆、文旅融合等项目制资助</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>降低运营与内容成本</t>
+          <t>补贴部分内容与活动成本</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>列政策匹配表→按窗口期申报→审计合规台账</t>
+          <t>政策匹配表→窗口期申报→验收审计台账</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -3123,22 +3098,22 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>世界人工智能大会（WAIC）资源延伸</t>
+          <t>重大展会会后延伸</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>会后365天常态化展示，承接展会溢出</t>
+          <t>城市级人工智能相关展会结束后，常设空间可承接部分展示与活动</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>内容新鲜度与城市品牌绑定</t>
+          <t>内容更新与城市品牌联动</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>对接大会组委会/承办方→会后巡展协议→常设展更新机制</t>
+          <t>对接承办/组委会→会后合作备忘→常设更新机制</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -3156,22 +3131,22 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>产业引导基金/央国企科创考核</t>
+          <t>产业引导基金与央国企合作</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>华润等央国企有科创投入与汇报需求</t>
+          <t>符合条件的可谈引导基金或战略合作出资</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>主赞助与跟投资金</t>
+          <t>补充开办或跟投资金</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>对齐对方考核指标写立项→董事会/办公会材料→出资协议</t>
+          <t>对齐对方考核与风控→立项材料→协议</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -3233,22 +3208,22 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>场地免租/租金补贴</t>
+          <t>租金优惠/装修支持</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>区属平台、国企闲置物业政策</t>
+          <t>区属平台、国企物业政策</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>建设期最大头成本</t>
+          <t>开办期租金与基础改造</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>框架协议优先</t>
+          <t>写入租约优先</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr"/>
@@ -3262,22 +3237,22 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>装修与设备配套</t>
+          <t>科普/科协相关经费</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>场地方出资约5000万谈判项</t>
+          <t>科协及科普专项</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>展陈与基建</t>
+          <t>科普活动、部分内容制作</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>与场地捆绑签约</t>
+          <t>年度申报</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr"/>
@@ -3291,22 +3266,22 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>科普/科协专项</t>
+          <t>研学/教育相关支持</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>科协系统</t>
+          <t>教育与相关主管部门</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>展陈内容、科普活动</t>
+          <t>课程、师资、接待条件改善</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>年度申报</t>
+          <t>学期前</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr"/>
@@ -3320,22 +3295,22 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>研学/教育专项</t>
+          <t>科创产业扶持</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>教育主管部门</t>
+          <t>区科创/经信</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>课程、师资、接待设施</t>
+          <t>孵化空间、活动、设备（视目录）</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>学期前</t>
+          <t>批次申报</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>
@@ -3349,22 +3324,22 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>科创产业扶持</t>
+          <t>文旅融合项目</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>区科创委/经信</t>
+          <t>文旅部门</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>孵化空间、算力、活动</t>
+          <t>观众服务、品牌活动</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>批次申报</t>
+          <t>项目制</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr"/>
@@ -3378,22 +3353,22 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>文旅融合/文创</t>
+          <t>产业引导基金</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>文旅部门</t>
+          <t>区级/央企基金</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>观众服务、品牌活动</t>
+          <t>符合投向的跟投或主体融资</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>项目制</t>
+          <t>立项后</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr"/>
@@ -3403,35 +3378,6 @@
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>产业引导基金</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>区级基金/央企基金</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>入驻项目跟投</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>设立后持续</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3444,7 +3390,7 @@
     <dataValidation sqref="F6:F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未开始,进行中,已完成,阻塞,取消"</formula1>
     </dataValidation>
-    <dataValidation sqref="F16:F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F16:F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未开始,进行中,已完成,阻塞,取消"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3480,7 +3426,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>谈判核心：免租10–20年 + 约5000万设备装修</t>
+          <t>谈判核心：租期与租金阶梯、装修分摊、退出条款</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3480,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>约3300㎡（小于理想总量，可作一期）</t>
+          <t>约3300㎡，适合作为一期试点</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -3544,12 +3490,12 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>地段好、研学便利；面积偏紧</t>
+          <t>地段好、研学便利；需谈清租期、租金优惠与装修分摊</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>正式需求书+免租与5000万条款路演</t>
+          <t>投资测算+需求书路演，比选租约条款</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -3561,7 +3507,7 @@
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>复兴岛场地</t>
+          <t>复兴岛相关物业</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -3571,7 +3517,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>具备改造条件；距陆家嘴约25分钟</t>
+          <t>具备改造条件；距陆家嘴车程约25分钟</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -3581,7 +3527,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>空间可塑性强；交通相对弱于五角场校区带</t>
+          <t>空间可塑性强；通学研学动线弱于五角场校区带</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -3605,7 +3551,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>对场地方：盘活闲置 + 高层考察场景 + 剩余面积招商优先/租金分成</t>
+          <t>对场地方：物业去化 + 可租面积分成 + 合理租金阶梯/装修期减免（写进租约）</t>
         </is>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -3618,7 +3564,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>对区政府：WAIC会后365天政绩 + 研学指标 + 科创名片</t>
+          <t>对区平台：科普/研学场景 + 重点项目申报材料，专项未批不计入必达资金</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -3631,7 +3577,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>对资方：科创考核故事 + AI历史席位（比广告好立项）</t>
+          <t>对赞助方：可报价权益包 + 可验收露出，合同约定合作期限</t>
         </is>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -3644,7 +3590,7 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>红线：建设期项目方尽量零出资本金；先封闭场地与设备资金再画施工图</t>
+          <t>红线：开办资金须覆盖预算；不以超长期零租金或大额无偿出资作为立项前提</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -3679,7 +3625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3693,21 +3639,21 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>展陈分层与资源对接</t>
+          <t>内容结构与资源对接</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>美方理论 / 中方应用</t>
+          <t>可签约 / 可授权 / 可更新</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>层级</t>
+          <t>板块</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3717,12 +3663,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>展品来源</t>
+          <t>主要来源</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>叙事</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -3739,22 +3685,22 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>芯片/算力/材料层</t>
+          <t>基础设施</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>芯片、服务器、算力基础设施（含低成本小型AI服务器趋势）</t>
+          <t>算力、芯片与基础系统演进（可展实物/图示）</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>国内外硬件与云厂商</t>
+          <t>硬件与云相关企业</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>AI基础设施史</t>
+          <t>强调可说明、可授权</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr"/>
@@ -3767,22 +3713,22 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>技术应用层</t>
+          <t>模型与工具</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>大模型、代码辅助、企业应用</t>
+          <t>通用模型与开发工具的产业应用</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>国内头部大模型企业为主</t>
+          <t>在沪科技企业为主</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>中国应用优势</t>
+          <t>以签约展位落地</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr"/>
@@ -3795,54 +3741,26 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>具身/移动/行业层</t>
+          <t>行业应用</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>机器人、无人机、教育、航海、行业场景</t>
+          <t>教育、制造、交通等已落地案例</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>具身智能与行业解决方案商</t>
+          <t>行业解决方案商</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>产业落地</t>
+          <t>避免概念演示充数</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>中美对照叙事</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>美方理论前沿 vs 中方产业应用</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>硅谷企业/高校 + 国内头部</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>实时连线与内容更新</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
@@ -3854,7 +3772,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未开始,进行中,已完成,阻塞,取消"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3868,7 +3786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3888,7 +3806,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>中美双团队推进</t>
+          <t>陈胜 · 胡继刚 · 陈红苗</t>
         </is>
       </c>
     </row>
@@ -3922,17 +3840,17 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>顶层主管</t>
+          <t>方案发起/海外线索</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>中国科协（目标）</t>
+          <t>陈胜</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>名称IP、行业合法性、专项与全国复制</t>
+          <t>海外授权线索、方案补充、博物馆运营经验访谈</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
@@ -3945,17 +3863,17 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>发起/海外资源</t>
+          <t>国内统筹</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>陈院长及美西团队</t>
+          <t>胡继刚</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>硅谷对接、海外展陈与内容、补充方案</t>
+          <t>方案文本、政府与场地资方路演材料、整体日程</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
@@ -3968,17 +3886,17 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>国内统筹</t>
+          <t>场地与资方对接</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>胡老师+国内团队</t>
+          <t>陈红苗</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>方案文本、政府与场地资方路演、日程</t>
+          <t>场地谈判配合、资方沟通、教育与渠道对接</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
@@ -3991,7 +3909,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>场地与建设</t>
+          <t>物业与工程</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -4001,7 +3919,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>免租物业、装修设备出资、工程</t>
+          <t>租约、改造工程、交付标准</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr"/>
@@ -4014,17 +3932,17 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>主赞助/资本</t>
+          <t>主赞助/战略资本</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>华润等意向央国企</t>
+          <t>意向央国企等</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>核心费用或场地、科创叙事</t>
+          <t>赞助或战略合作出资</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
@@ -4037,44 +3955,21 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>生态合作</t>
+          <t>运营公司</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>曾达等AI布局方、头部企业</t>
+          <t>待设运营主体</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>展陈、流量、产业协同</t>
+          <t>日常运营、招商、研学、财务管理</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>运营公司</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>待设轻资产主体</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>日常运营、招商、研学、孵化投资执行</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
@@ -4086,7 +3981,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未开始,进行中,已完成,阻塞,取消"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4121,7 +4016,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>谈判与预算为当前最高优先级风险</t>
+          <t>租金条款与开办资金闭环为当前最高优先级</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4055,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>场地免租+出资谈判失败</t>
+          <t>租金与装修谈判达不成</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -4170,12 +4065,12 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>核心难点在谈判</t>
+          <t>优惠幅度不足则开办成本过高</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>多场地并行；权益包量化政绩与租金分成</t>
+          <t>双场地并行；准备保底租金方案与缩期一期</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr"/>
@@ -4188,22 +4083,22 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>单一政府/企业无法独扛</t>
+          <t>开办资金闭环失败</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>体制局限或号召力不足</t>
+          <t>赞助与专项不及预期</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>第三方整合+科协背书+分层赞助</t>
+          <t>启动金底线+分期开业；砍非必要展陈</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr"/>
@@ -4216,22 +4111,22 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>中美内容双向同步受限</t>
+          <t>把政策当成已兑现收入</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>需确认美方接受度</t>
+          <t>申报有窗口与不确定性</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>授权分级；理论/应用分展区；合规审查</t>
+          <t>预算中专项只计保守到账比例</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
@@ -4244,22 +4139,22 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>预算不清导致推进空转</t>
+          <t>与现有科技展厅同质化</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>无清晰预算难闭环资方</t>
+          <t>曹河泾/张江等已有展陈</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>先出大框架预算再施工图</t>
+          <t>强化研学服务与企业展位运营，而非概念堆砌</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr"/>
@@ -4272,7 +4167,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>与现有机器人展厅同质化</t>
+          <t>内容授权与合规</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -4282,12 +4177,12 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>曹河泾/张江已有展厅</t>
+          <t>涉外与企业品牌使用限制</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>强调全产业链+历史叙事+中美实时+孵化</t>
+          <t>先签授权再制作；法务预审</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr"/>
@@ -4300,7 +4195,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>研学政策执行不及预期</t>
+          <t>研学招生不及预期</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -4310,12 +4205,12 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>地方落地节奏不一</t>
+          <t>学期节奏与采购周期</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>多区试点；B端机构双轮</t>
+          <t>机构渠道双轮；淡季靠企业活动补</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr"/>

--- a/deliverables/上海AI博物馆_投资盈利政策落地表.xlsx
+++ b/deliverables/上海AI博物馆_投资盈利政策落地表.xlsx
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>一期建议控制在可运营规模：展示区约1500–3000㎡，或先落创智汇约3300㎡顶楼作试点；若后续扩展至更大体量，需单独做投资测算。租金、装修与设备以「共担+分期」谈判，不把长期免租或场地方大额无偿出资作为前提。</t>
+          <t>一期建议控制在可运营规模：展示区约1500–3000㎡，或先落创智汇约3300㎡顶楼作试点；若后续扩展至更大体量，需单独做投资测算。租金、装修与设备以「共担+分期」谈判，不以超长期零租金或场地方大额无偿出资作为前提。</t>
         </is>
       </c>
     </row>
